--- a/data/controles_results/dif_medias/controls_vars/difmedias_controles_baselines_fixed_2018_T4_2.xlsx
+++ b/data/controles_results/dif_medias/controls_vars/difmedias_controles_baselines_fixed_2018_T4_2.xlsx
@@ -57,10 +57,10 @@
     <t>N</t>
   </si>
   <si>
-    <t>86</t>
-  </si>
-  <si>
-    <t>85</t>
+    <t>56</t>
+  </si>
+  <si>
+    <t>55</t>
   </si>
   <si>
     <t xml:space="preserve"> (1) </t>
@@ -72,67 +72,67 @@
     <t>Mean/(SE)</t>
   </si>
   <si>
-    <t>5.98e+05</t>
-  </si>
-  <si>
-    <t>(76129.348)</t>
-  </si>
-  <si>
-    <t>501.971</t>
-  </si>
-  <si>
-    <t>(33.457)</t>
-  </si>
-  <si>
-    <t>3.577</t>
-  </si>
-  <si>
-    <t>(0.043)</t>
-  </si>
-  <si>
-    <t>11.709</t>
-  </si>
-  <si>
-    <t>(1.740)</t>
-  </si>
-  <si>
-    <t>88.861</t>
-  </si>
-  <si>
-    <t>(0.438)</t>
-  </si>
-  <si>
-    <t>1.09e+06</t>
-  </si>
-  <si>
-    <t>(52024.658)</t>
-  </si>
-  <si>
-    <t>2.616</t>
-  </si>
-  <si>
-    <t>(0.118)</t>
-  </si>
-  <si>
-    <t>3.581</t>
-  </si>
-  <si>
-    <t>(0.413)</t>
-  </si>
-  <si>
-    <t>34.512</t>
-  </si>
-  <si>
-    <t>(3.202)</t>
-  </si>
-  <si>
-    <t>0.977</t>
-  </si>
-  <si>
-    <t>(0.016)</t>
-  </si>
-  <si>
-    <t>28</t>
+    <t>5.24e+05</t>
+  </si>
+  <si>
+    <t>(80953.804)</t>
+  </si>
+  <si>
+    <t>503.534</t>
+  </si>
+  <si>
+    <t>(38.331)</t>
+  </si>
+  <si>
+    <t>3.714</t>
+  </si>
+  <si>
+    <t>(0.049)</t>
+  </si>
+  <si>
+    <t>6.411</t>
+  </si>
+  <si>
+    <t>(1.336)</t>
+  </si>
+  <si>
+    <t>87.003</t>
+  </si>
+  <si>
+    <t>(0.512)</t>
+  </si>
+  <si>
+    <t>8.97e+05</t>
+  </si>
+  <si>
+    <t>(55836.359)</t>
+  </si>
+  <si>
+    <t>2.162</t>
+  </si>
+  <si>
+    <t>(0.135)</t>
+  </si>
+  <si>
+    <t>2.339</t>
+  </si>
+  <si>
+    <t>(0.404)</t>
+  </si>
+  <si>
+    <t>29.286</t>
+  </si>
+  <si>
+    <t>(4.490)</t>
+  </si>
+  <si>
+    <t>0.929</t>
+  </si>
+  <si>
+    <t>(0.035)</t>
+  </si>
+  <si>
+    <t>60</t>
   </si>
   <si>
     <t xml:space="preserve"> (2) </t>
@@ -141,58 +141,58 @@
     <t>1</t>
   </si>
   <si>
-    <t>7.04e+05</t>
-  </si>
-  <si>
-    <t>(1.33e+05)</t>
-  </si>
-  <si>
-    <t>476.691</t>
-  </si>
-  <si>
-    <t>(63.786)</t>
-  </si>
-  <si>
-    <t>3.299</t>
-  </si>
-  <si>
-    <t>(0.071)</t>
-  </si>
-  <si>
-    <t>30.429</t>
-  </si>
-  <si>
-    <t>(5.333)</t>
-  </si>
-  <si>
-    <t>91.249</t>
-  </si>
-  <si>
-    <t>(0.593)</t>
-  </si>
-  <si>
-    <t>1.37e+06</t>
-  </si>
-  <si>
-    <t>(87943.642)</t>
-  </si>
-  <si>
-    <t>3.408</t>
-  </si>
-  <si>
-    <t>(0.188)</t>
-  </si>
-  <si>
-    <t>6.679</t>
-  </si>
-  <si>
-    <t>(0.784)</t>
-  </si>
-  <si>
-    <t>47.286</t>
-  </si>
-  <si>
-    <t>(4.289)</t>
+    <t>6.98e+05</t>
+  </si>
+  <si>
+    <t>(1.00e+05)</t>
+  </si>
+  <si>
+    <t>482.463</t>
+  </si>
+  <si>
+    <t>(43.823)</t>
+  </si>
+  <si>
+    <t>3.335</t>
+  </si>
+  <si>
+    <t>(0.048)</t>
+  </si>
+  <si>
+    <t>25.000</t>
+  </si>
+  <si>
+    <t>(3.191)</t>
+  </si>
+  <si>
+    <t>91.511</t>
+  </si>
+  <si>
+    <t>(0.367)</t>
+  </si>
+  <si>
+    <t>1.38e+06</t>
+  </si>
+  <si>
+    <t>(57218.217)</t>
+  </si>
+  <si>
+    <t>3.352</t>
+  </si>
+  <si>
+    <t>(0.119)</t>
+  </si>
+  <si>
+    <t>6.067</t>
+  </si>
+  <si>
+    <t>(0.544)</t>
+  </si>
+  <si>
+    <t>44.200</t>
+  </si>
+  <si>
+    <t>(2.738)</t>
   </si>
   <si>
     <t>1.000</t>
@@ -201,10 +201,10 @@
     <t>(0.000)</t>
   </si>
   <si>
-    <t>114</t>
-  </si>
-  <si>
-    <t>113</t>
+    <t>116</t>
+  </si>
+  <si>
+    <t>115</t>
   </si>
   <si>
     <t>(2)-(1)</t>
@@ -216,34 +216,34 @@
     <t>Mean difference</t>
   </si>
   <si>
-    <t>1.06e+05</t>
-  </si>
-  <si>
-    <t>-25.280</t>
-  </si>
-  <si>
-    <t>-0.278***</t>
-  </si>
-  <si>
-    <t>18.719***</t>
-  </si>
-  <si>
-    <t>2.388***</t>
-  </si>
-  <si>
-    <t>2.77e+05***</t>
-  </si>
-  <si>
-    <t>0.792***</t>
-  </si>
-  <si>
-    <t>3.097***</t>
-  </si>
-  <si>
-    <t>12.774**</t>
-  </si>
-  <si>
-    <t>0.023</t>
+    <t>1.74e+05</t>
+  </si>
+  <si>
+    <t>-21.071</t>
+  </si>
+  <si>
+    <t>-0.380***</t>
+  </si>
+  <si>
+    <t>18.589***</t>
+  </si>
+  <si>
+    <t>4.508***</t>
+  </si>
+  <si>
+    <t>4.82e+05***</t>
+  </si>
+  <si>
+    <t>1.190***</t>
+  </si>
+  <si>
+    <t>3.727***</t>
+  </si>
+  <si>
+    <t>14.914***</t>
+  </si>
+  <si>
+    <t>0.071**</t>
   </si>
 </sst>
 </file>

--- a/data/controles_results/dif_medias/controls_vars/difmedias_controles_baselines_fixed_2018_T4_2.xlsx
+++ b/data/controles_results/dif_medias/controls_vars/difmedias_controles_baselines_fixed_2018_T4_2.xlsx
@@ -57,10 +57,10 @@
     <t>N</t>
   </si>
   <si>
-    <t>56</t>
-  </si>
-  <si>
-    <t>55</t>
+    <t>86</t>
+  </si>
+  <si>
+    <t>85</t>
   </si>
   <si>
     <t xml:space="preserve"> (1) </t>
@@ -72,67 +72,67 @@
     <t>Mean/(SE)</t>
   </si>
   <si>
-    <t>5.24e+05</t>
-  </si>
-  <si>
-    <t>(80953.804)</t>
-  </si>
-  <si>
-    <t>503.534</t>
-  </si>
-  <si>
-    <t>(38.331)</t>
-  </si>
-  <si>
-    <t>3.714</t>
-  </si>
-  <si>
-    <t>(0.049)</t>
-  </si>
-  <si>
-    <t>6.411</t>
-  </si>
-  <si>
-    <t>(1.336)</t>
-  </si>
-  <si>
-    <t>87.003</t>
-  </si>
-  <si>
-    <t>(0.512)</t>
-  </si>
-  <si>
-    <t>8.97e+05</t>
-  </si>
-  <si>
-    <t>(55836.359)</t>
-  </si>
-  <si>
-    <t>2.162</t>
-  </si>
-  <si>
-    <t>(0.135)</t>
-  </si>
-  <si>
-    <t>2.339</t>
-  </si>
-  <si>
-    <t>(0.404)</t>
-  </si>
-  <si>
-    <t>29.286</t>
-  </si>
-  <si>
-    <t>(4.490)</t>
-  </si>
-  <si>
-    <t>0.929</t>
-  </si>
-  <si>
-    <t>(0.035)</t>
-  </si>
-  <si>
-    <t>60</t>
+    <t>5.98e+05</t>
+  </si>
+  <si>
+    <t>(76129.348)</t>
+  </si>
+  <si>
+    <t>501.971</t>
+  </si>
+  <si>
+    <t>(33.457)</t>
+  </si>
+  <si>
+    <t>3.577</t>
+  </si>
+  <si>
+    <t>(0.043)</t>
+  </si>
+  <si>
+    <t>11.709</t>
+  </si>
+  <si>
+    <t>(1.740)</t>
+  </si>
+  <si>
+    <t>88.861</t>
+  </si>
+  <si>
+    <t>(0.438)</t>
+  </si>
+  <si>
+    <t>1.09e+06</t>
+  </si>
+  <si>
+    <t>(52024.658)</t>
+  </si>
+  <si>
+    <t>2.616</t>
+  </si>
+  <si>
+    <t>(0.118)</t>
+  </si>
+  <si>
+    <t>3.581</t>
+  </si>
+  <si>
+    <t>(0.413)</t>
+  </si>
+  <si>
+    <t>34.512</t>
+  </si>
+  <si>
+    <t>(3.202)</t>
+  </si>
+  <si>
+    <t>0.977</t>
+  </si>
+  <si>
+    <t>(0.016)</t>
+  </si>
+  <si>
+    <t>28</t>
   </si>
   <si>
     <t xml:space="preserve"> (2) </t>
@@ -141,58 +141,58 @@
     <t>1</t>
   </si>
   <si>
-    <t>6.98e+05</t>
-  </si>
-  <si>
-    <t>(1.00e+05)</t>
-  </si>
-  <si>
-    <t>482.463</t>
-  </si>
-  <si>
-    <t>(43.823)</t>
-  </si>
-  <si>
-    <t>3.335</t>
-  </si>
-  <si>
-    <t>(0.048)</t>
-  </si>
-  <si>
-    <t>25.000</t>
-  </si>
-  <si>
-    <t>(3.191)</t>
-  </si>
-  <si>
-    <t>91.511</t>
-  </si>
-  <si>
-    <t>(0.367)</t>
-  </si>
-  <si>
-    <t>1.38e+06</t>
-  </si>
-  <si>
-    <t>(57218.217)</t>
-  </si>
-  <si>
-    <t>3.352</t>
-  </si>
-  <si>
-    <t>(0.119)</t>
-  </si>
-  <si>
-    <t>6.067</t>
-  </si>
-  <si>
-    <t>(0.544)</t>
-  </si>
-  <si>
-    <t>44.200</t>
-  </si>
-  <si>
-    <t>(2.738)</t>
+    <t>7.04e+05</t>
+  </si>
+  <si>
+    <t>(1.33e+05)</t>
+  </si>
+  <si>
+    <t>476.691</t>
+  </si>
+  <si>
+    <t>(63.786)</t>
+  </si>
+  <si>
+    <t>3.299</t>
+  </si>
+  <si>
+    <t>(0.071)</t>
+  </si>
+  <si>
+    <t>30.429</t>
+  </si>
+  <si>
+    <t>(5.333)</t>
+  </si>
+  <si>
+    <t>91.249</t>
+  </si>
+  <si>
+    <t>(0.593)</t>
+  </si>
+  <si>
+    <t>1.37e+06</t>
+  </si>
+  <si>
+    <t>(87943.642)</t>
+  </si>
+  <si>
+    <t>3.408</t>
+  </si>
+  <si>
+    <t>(0.188)</t>
+  </si>
+  <si>
+    <t>6.679</t>
+  </si>
+  <si>
+    <t>(0.784)</t>
+  </si>
+  <si>
+    <t>47.286</t>
+  </si>
+  <si>
+    <t>(4.289)</t>
   </si>
   <si>
     <t>1.000</t>
@@ -201,10 +201,10 @@
     <t>(0.000)</t>
   </si>
   <si>
-    <t>116</t>
-  </si>
-  <si>
-    <t>115</t>
+    <t>114</t>
+  </si>
+  <si>
+    <t>113</t>
   </si>
   <si>
     <t>(2)-(1)</t>
@@ -216,34 +216,34 @@
     <t>Mean difference</t>
   </si>
   <si>
-    <t>1.74e+05</t>
-  </si>
-  <si>
-    <t>-21.071</t>
-  </si>
-  <si>
-    <t>-0.380***</t>
-  </si>
-  <si>
-    <t>18.589***</t>
-  </si>
-  <si>
-    <t>4.508***</t>
-  </si>
-  <si>
-    <t>4.82e+05***</t>
-  </si>
-  <si>
-    <t>1.190***</t>
-  </si>
-  <si>
-    <t>3.727***</t>
-  </si>
-  <si>
-    <t>14.914***</t>
-  </si>
-  <si>
-    <t>0.071**</t>
+    <t>1.06e+05</t>
+  </si>
+  <si>
+    <t>-25.280</t>
+  </si>
+  <si>
+    <t>-0.278***</t>
+  </si>
+  <si>
+    <t>18.719***</t>
+  </si>
+  <si>
+    <t>2.388***</t>
+  </si>
+  <si>
+    <t>2.77e+05***</t>
+  </si>
+  <si>
+    <t>0.792***</t>
+  </si>
+  <si>
+    <t>3.097***</t>
+  </si>
+  <si>
+    <t>12.774**</t>
+  </si>
+  <si>
+    <t>0.023</t>
   </si>
 </sst>
 </file>
